--- a/verification/report-samples/oil.xlsx
+++ b/verification/report-samples/oil.xlsx
@@ -7,7 +7,7 @@
     <sheet sheetId="1" name="Report" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A1:$CF11</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A1:$CF15</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Report'!$1:$8</definedName>
   </definedNames>
   <calcPr calcId="171027"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
   <si>
     <t>Gujjar Brother Transport — TEST DATA ONLY</t>
   </si>
@@ -26,7 +26,7 @@
     <t>VEHICLES OIL CHANGE RECORD · TEST accounting period</t>
   </si>
   <si>
-    <t>2026-01-01 to 2026-12-31 · PKR · 2026-10-06T19:37:02.286+00:00</t>
+    <t>2026-01-01 to 2026-12-31 · PKR · 2026-10-11T16:34:22.474+00:00</t>
   </si>
   <si>
     <t>Selected authorized records</t>
@@ -56,7 +56,7 @@
     <t>Closing Meter (km)</t>
   </si>
   <si>
-    <t>Travel after Oil Change(km)</t>
+    <t>Travel after oil change (km)</t>
   </si>
   <si>
     <t>DRIVER</t>
@@ -66,6 +66,17 @@
   </si>
   <si>
     <t>TEST Driver</t>
+  </si>
+  <si>
+    <t>Driver signature</t>
+  </si>
+  <si>
+    <t>Authorized officer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Signature: __________________
+Name: ____________________
+Date: _____________________</t>
   </si>
   <si>
     <t>One row per vehicle: latest approved oil change through period end; previous stored reading or preceding approved change. Closing meter uses dated approved trip/maintenance observations through the cutoff, never today’s vehicle meter.</t>
@@ -563,7 +574,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CF11"/>
+  <dimension ref="A1:CF15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="84" width="1.35" customWidth="1"/>
@@ -1309,96 +1320,364 @@
       <c r="CE9" s="6"/>
       <c r="CF9" s="6"/>
     </row>
-    <row r="11" ht="30" customHeight="1" spans="1:84" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+    <row r="11" ht="22" customHeight="1" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+      <c r="S11" s="3"/>
+      <c r="T11" s="3"/>
+      <c r="U11" s="3"/>
+      <c r="V11" s="3"/>
+      <c r="W11" s="3"/>
+      <c r="X11" s="3"/>
+      <c r="Y11" s="3"/>
+      <c r="Z11" s="3"/>
+      <c r="AA11" s="3"/>
+      <c r="AB11" s="3"/>
+      <c r="AC11" s="3"/>
+      <c r="AD11" s="3"/>
+      <c r="AE11" s="3"/>
+      <c r="AF11" s="3"/>
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3"/>
+      <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
+      <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
+      <c r="AR11" s="3"/>
+      <c r="AS11" s="3"/>
+      <c r="AT11" s="3"/>
+      <c r="AU11" s="3"/>
+      <c r="AV11" s="3"/>
+      <c r="AW11" s="3"/>
+      <c r="AX11" s="3"/>
+      <c r="AY11" s="3"/>
+      <c r="AZ11" s="3"/>
+      <c r="BA11" s="3"/>
+      <c r="BB11" s="3"/>
+      <c r="BC11" s="3"/>
+      <c r="BD11" s="3"/>
+      <c r="BE11" s="3"/>
+      <c r="BF11" s="3"/>
+      <c r="BG11" s="3"/>
+      <c r="BH11" s="3"/>
+      <c r="BI11" s="3"/>
+      <c r="BJ11" s="3"/>
+      <c r="BK11" s="3"/>
+      <c r="BL11" s="3"/>
+      <c r="BM11" s="3"/>
+      <c r="BN11" s="3"/>
+      <c r="BO11" s="3"/>
+      <c r="BP11" s="3"/>
+      <c r="BQ11" s="3"/>
+      <c r="BR11" s="3"/>
+      <c r="BS11" s="3"/>
+      <c r="BT11" s="3"/>
+      <c r="BU11" s="3"/>
+      <c r="BV11" s="3"/>
+      <c r="BW11" s="3"/>
+      <c r="BX11" s="3"/>
+      <c r="BY11" s="3"/>
+      <c r="BZ11" s="3"/>
+      <c r="CA11" s="3"/>
+      <c r="CB11" s="3"/>
+      <c r="CC11" s="3"/>
+      <c r="CD11" s="3"/>
+      <c r="CE11" s="3"/>
+      <c r="CF11" s="3"/>
+    </row>
+    <row r="12" ht="45" customHeight="1" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2"/>
-      <c r="Q11" s="2"/>
-      <c r="R11" s="2"/>
-      <c r="S11" s="2"/>
-      <c r="T11" s="2"/>
-      <c r="U11" s="2"/>
-      <c r="V11" s="2"/>
-      <c r="W11" s="2"/>
-      <c r="X11" s="2"/>
-      <c r="Y11" s="2"/>
-      <c r="Z11" s="2"/>
-      <c r="AA11" s="2"/>
-      <c r="AB11" s="2"/>
-      <c r="AC11" s="2"/>
-      <c r="AD11" s="2"/>
-      <c r="AE11" s="2"/>
-      <c r="AF11" s="2"/>
-      <c r="AG11" s="2"/>
-      <c r="AH11" s="2"/>
-      <c r="AI11" s="2"/>
-      <c r="AJ11" s="2"/>
-      <c r="AK11" s="2"/>
-      <c r="AL11" s="2"/>
-      <c r="AM11" s="2"/>
-      <c r="AN11" s="2"/>
-      <c r="AO11" s="2"/>
-      <c r="AP11" s="2"/>
-      <c r="AQ11" s="2"/>
-      <c r="AR11" s="2"/>
-      <c r="AS11" s="2"/>
-      <c r="AT11" s="2"/>
-      <c r="AU11" s="2"/>
-      <c r="AV11" s="2"/>
-      <c r="AW11" s="2"/>
-      <c r="AX11" s="2"/>
-      <c r="AY11" s="2"/>
-      <c r="AZ11" s="2"/>
-      <c r="BA11" s="2"/>
-      <c r="BB11" s="2"/>
-      <c r="BC11" s="2"/>
-      <c r="BD11" s="2"/>
-      <c r="BE11" s="2"/>
-      <c r="BF11" s="2"/>
-      <c r="BG11" s="2"/>
-      <c r="BH11" s="2"/>
-      <c r="BI11" s="2"/>
-      <c r="BJ11" s="2"/>
-      <c r="BK11" s="2"/>
-      <c r="BL11" s="2"/>
-      <c r="BM11" s="2"/>
-      <c r="BN11" s="2"/>
-      <c r="BO11" s="2"/>
-      <c r="BP11" s="2"/>
-      <c r="BQ11" s="2"/>
-      <c r="BR11" s="2"/>
-      <c r="BS11" s="2"/>
-      <c r="BT11" s="2"/>
-      <c r="BU11" s="2"/>
-      <c r="BV11" s="2"/>
-      <c r="BW11" s="2"/>
-      <c r="BX11" s="2"/>
-      <c r="BY11" s="2"/>
-      <c r="BZ11" s="2"/>
-      <c r="CA11" s="2"/>
-      <c r="CB11" s="2"/>
-      <c r="CC11" s="2"/>
-      <c r="CD11" s="2"/>
-      <c r="CE11" s="2"/>
-      <c r="CF11" s="2"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="3"/>
+      <c r="N12" s="3"/>
+      <c r="O12" s="3"/>
+      <c r="P12" s="3"/>
+      <c r="Q12" s="3"/>
+      <c r="R12" s="3"/>
+      <c r="S12" s="3"/>
+      <c r="T12" s="3"/>
+      <c r="U12" s="3"/>
+      <c r="V12" s="3"/>
+      <c r="W12" s="3"/>
+      <c r="X12" s="3"/>
+      <c r="Y12" s="3"/>
+      <c r="Z12" s="3"/>
+      <c r="AA12" s="3"/>
+      <c r="AB12" s="3"/>
+      <c r="AC12" s="3"/>
+      <c r="AD12" s="3"/>
+      <c r="AE12" s="3"/>
+      <c r="AF12" s="3"/>
+      <c r="AG12" s="3"/>
+      <c r="AH12" s="3"/>
+      <c r="AI12" s="3"/>
+      <c r="AJ12" s="3"/>
+      <c r="AK12" s="3"/>
+      <c r="AL12" s="3"/>
+      <c r="AM12" s="3"/>
+      <c r="AN12" s="3"/>
+      <c r="AO12" s="3"/>
+      <c r="AP12" s="3"/>
+      <c r="AQ12" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="AR12" s="3"/>
+      <c r="AS12" s="3"/>
+      <c r="AT12" s="3"/>
+      <c r="AU12" s="3"/>
+      <c r="AV12" s="3"/>
+      <c r="AW12" s="3"/>
+      <c r="AX12" s="3"/>
+      <c r="AY12" s="3"/>
+      <c r="AZ12" s="3"/>
+      <c r="BA12" s="3"/>
+      <c r="BB12" s="3"/>
+      <c r="BC12" s="3"/>
+      <c r="BD12" s="3"/>
+      <c r="BE12" s="3"/>
+      <c r="BF12" s="3"/>
+      <c r="BG12" s="3"/>
+      <c r="BH12" s="3"/>
+      <c r="BI12" s="3"/>
+      <c r="BJ12" s="3"/>
+      <c r="BK12" s="3"/>
+      <c r="BL12" s="3"/>
+      <c r="BM12" s="3"/>
+      <c r="BN12" s="3"/>
+      <c r="BO12" s="3"/>
+      <c r="BP12" s="3"/>
+      <c r="BQ12" s="3"/>
+      <c r="BR12" s="3"/>
+      <c r="BS12" s="3"/>
+      <c r="BT12" s="3"/>
+      <c r="BU12" s="3"/>
+      <c r="BV12" s="3"/>
+      <c r="BW12" s="3"/>
+      <c r="BX12" s="3"/>
+      <c r="BY12" s="3"/>
+      <c r="BZ12" s="3"/>
+      <c r="CA12" s="3"/>
+      <c r="CB12" s="3"/>
+      <c r="CC12" s="3"/>
+      <c r="CD12" s="3"/>
+      <c r="CE12" s="3"/>
+      <c r="CF12" s="3"/>
+    </row>
+    <row r="13" ht="85" customHeight="1" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="6"/>
+      <c r="P13" s="6"/>
+      <c r="Q13" s="6"/>
+      <c r="R13" s="6"/>
+      <c r="S13" s="6"/>
+      <c r="T13" s="6"/>
+      <c r="U13" s="6"/>
+      <c r="V13" s="6"/>
+      <c r="W13" s="6"/>
+      <c r="X13" s="6"/>
+      <c r="Y13" s="6"/>
+      <c r="Z13" s="6"/>
+      <c r="AA13" s="6"/>
+      <c r="AB13" s="6"/>
+      <c r="AC13" s="6"/>
+      <c r="AD13" s="6"/>
+      <c r="AE13" s="6"/>
+      <c r="AF13" s="6"/>
+      <c r="AG13" s="6"/>
+      <c r="AH13" s="6"/>
+      <c r="AI13" s="6"/>
+      <c r="AJ13" s="6"/>
+      <c r="AK13" s="6"/>
+      <c r="AL13" s="6"/>
+      <c r="AM13" s="6"/>
+      <c r="AN13" s="6"/>
+      <c r="AO13" s="6"/>
+      <c r="AP13" s="6"/>
+      <c r="AQ13" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="AR13" s="6"/>
+      <c r="AS13" s="6"/>
+      <c r="AT13" s="6"/>
+      <c r="AU13" s="6"/>
+      <c r="AV13" s="6"/>
+      <c r="AW13" s="6"/>
+      <c r="AX13" s="6"/>
+      <c r="AY13" s="6"/>
+      <c r="AZ13" s="6"/>
+      <c r="BA13" s="6"/>
+      <c r="BB13" s="6"/>
+      <c r="BC13" s="6"/>
+      <c r="BD13" s="6"/>
+      <c r="BE13" s="6"/>
+      <c r="BF13" s="6"/>
+      <c r="BG13" s="6"/>
+      <c r="BH13" s="6"/>
+      <c r="BI13" s="6"/>
+      <c r="BJ13" s="6"/>
+      <c r="BK13" s="6"/>
+      <c r="BL13" s="6"/>
+      <c r="BM13" s="6"/>
+      <c r="BN13" s="6"/>
+      <c r="BO13" s="6"/>
+      <c r="BP13" s="6"/>
+      <c r="BQ13" s="6"/>
+      <c r="BR13" s="6"/>
+      <c r="BS13" s="6"/>
+      <c r="BT13" s="6"/>
+      <c r="BU13" s="6"/>
+      <c r="BV13" s="6"/>
+      <c r="BW13" s="6"/>
+      <c r="BX13" s="6"/>
+      <c r="BY13" s="6"/>
+      <c r="BZ13" s="6"/>
+      <c r="CA13" s="6"/>
+      <c r="CB13" s="6"/>
+      <c r="CC13" s="6"/>
+      <c r="CD13" s="6"/>
+      <c r="CE13" s="6"/>
+      <c r="CF13" s="6"/>
+    </row>
+    <row r="15" ht="30" customHeight="1" spans="1:84" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2"/>
+      <c r="S15" s="2"/>
+      <c r="T15" s="2"/>
+      <c r="U15" s="2"/>
+      <c r="V15" s="2"/>
+      <c r="W15" s="2"/>
+      <c r="X15" s="2"/>
+      <c r="Y15" s="2"/>
+      <c r="Z15" s="2"/>
+      <c r="AA15" s="2"/>
+      <c r="AB15" s="2"/>
+      <c r="AC15" s="2"/>
+      <c r="AD15" s="2"/>
+      <c r="AE15" s="2"/>
+      <c r="AF15" s="2"/>
+      <c r="AG15" s="2"/>
+      <c r="AH15" s="2"/>
+      <c r="AI15" s="2"/>
+      <c r="AJ15" s="2"/>
+      <c r="AK15" s="2"/>
+      <c r="AL15" s="2"/>
+      <c r="AM15" s="2"/>
+      <c r="AN15" s="2"/>
+      <c r="AO15" s="2"/>
+      <c r="AP15" s="2"/>
+      <c r="AQ15" s="2"/>
+      <c r="AR15" s="2"/>
+      <c r="AS15" s="2"/>
+      <c r="AT15" s="2"/>
+      <c r="AU15" s="2"/>
+      <c r="AV15" s="2"/>
+      <c r="AW15" s="2"/>
+      <c r="AX15" s="2"/>
+      <c r="AY15" s="2"/>
+      <c r="AZ15" s="2"/>
+      <c r="BA15" s="2"/>
+      <c r="BB15" s="2"/>
+      <c r="BC15" s="2"/>
+      <c r="BD15" s="2"/>
+      <c r="BE15" s="2"/>
+      <c r="BF15" s="2"/>
+      <c r="BG15" s="2"/>
+      <c r="BH15" s="2"/>
+      <c r="BI15" s="2"/>
+      <c r="BJ15" s="2"/>
+      <c r="BK15" s="2"/>
+      <c r="BL15" s="2"/>
+      <c r="BM15" s="2"/>
+      <c r="BN15" s="2"/>
+      <c r="BO15" s="2"/>
+      <c r="BP15" s="2"/>
+      <c r="BQ15" s="2"/>
+      <c r="BR15" s="2"/>
+      <c r="BS15" s="2"/>
+      <c r="BT15" s="2"/>
+      <c r="BU15" s="2"/>
+      <c r="BV15" s="2"/>
+      <c r="BW15" s="2"/>
+      <c r="BX15" s="2"/>
+      <c r="BY15" s="2"/>
+      <c r="BZ15" s="2"/>
+      <c r="CA15" s="2"/>
+      <c r="CB15" s="2"/>
+      <c r="CC15" s="2"/>
+      <c r="CD15" s="2"/>
+      <c r="CE15" s="2"/>
+      <c r="CF15" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="27">
+  <mergeCells count="32">
     <mergeCell ref="A1:CF1"/>
     <mergeCell ref="A2:CF2"/>
     <mergeCell ref="A3:CF3"/>
@@ -1426,6 +1705,11 @@
     <mergeCell ref="BM9:BX9"/>
     <mergeCell ref="BY9:CF9"/>
     <mergeCell ref="A11:CF11"/>
+    <mergeCell ref="A12:AP12"/>
+    <mergeCell ref="AQ12:CF12"/>
+    <mergeCell ref="A13:AP13"/>
+    <mergeCell ref="AQ13:CF13"/>
+    <mergeCell ref="A15:CF15"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.3" bottom="0.3" header="0.1" footer="0.1"/>
